--- a/docs/design/ACSMS-SCR-022/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_ファイルダウンロード画面_v1.1.xlsx
+++ b/docs/design/ACSMS-SCR-022/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_ファイルダウンロード画面_v1.1.xlsx
@@ -1200,7 +1200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH3"/>
+  <dimension ref="A1:AH4"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="3.33" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1415,26 +1415,86 @@
       <c r="AG3" s="10" t="n"/>
       <c r="AH3" s="11" t="n"/>
     </row>
+    <row r="4" ht="22.5" customHeight="1">
+      <c r="A4" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="11" t="n"/>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="n"/>
+      <c r="H4" s="11" t="n"/>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="n"/>
+      <c r="K4" s="10" t="n"/>
+      <c r="L4" s="10" t="n"/>
+      <c r="M4" s="10" t="n"/>
+      <c r="N4" s="11" t="n"/>
+      <c r="O4" s="20" t="inlineStr">
+        <is>
+          <t>実装との差分是正（顧客要件2026-07の2件が未反映だった）：①TC-003 を中央会の新DataScope（同一都道府県の全JA／#52132）へ書き換え。従来の「自中央会+管轄JA」記述は実装と一致しなくなっていた。②カテゴリ9を新設し2件追加（TC-059〜060）。059＝県スコープ拡大の一覧・個別DL・プレビュー・ZIP、`todofuken_code` 未設定セッションの自JAフォールバック、JA本店/JA管理支店へ広がらないこと、FEのJA絞り込み候補。060＝日農DL許可=false のDL制限ロールに中央会を追加したこと、および自分が出力したファイルは本フラグを見ない例外（`created_by` 空文字は本人扱いしない）</t>
+        </is>
+      </c>
+      <c r="P4" s="10" t="n"/>
+      <c r="Q4" s="10" t="n"/>
+      <c r="R4" s="10" t="n"/>
+      <c r="S4" s="10" t="n"/>
+      <c r="T4" s="10" t="n"/>
+      <c r="U4" s="10" t="n"/>
+      <c r="V4" s="11" t="n"/>
+      <c r="W4" s="19" t="inlineStr"/>
+      <c r="X4" s="10" t="n"/>
+      <c r="Y4" s="10" t="n"/>
+      <c r="Z4" s="10" t="n"/>
+      <c r="AA4" s="10" t="n"/>
+      <c r="AB4" s="11" t="n"/>
+      <c r="AC4" s="19" t="inlineStr"/>
+      <c r="AD4" s="10" t="n"/>
+      <c r="AE4" s="10" t="n"/>
+      <c r="AF4" s="10" t="n"/>
+      <c r="AG4" s="10" t="n"/>
+      <c r="AH4" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="24">
+    <mergeCell ref="O3:V3"/>
+    <mergeCell ref="W1:AB1"/>
+    <mergeCell ref="W3:AB3"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="I3:N3"/>
+    <mergeCell ref="AC4:AH4"/>
+    <mergeCell ref="AC1:AH1"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="O1:V1"/>
+    <mergeCell ref="I1:N1"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="I4:N4"/>
+    <mergeCell ref="O4:V4"/>
+    <mergeCell ref="W2:AB2"/>
+    <mergeCell ref="AC2:AH2"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="W4:AB4"/>
     <mergeCell ref="B1:E1"/>
-    <mergeCell ref="AC2:AH2"/>
-    <mergeCell ref="AC1:AH1"/>
-    <mergeCell ref="O3:V3"/>
     <mergeCell ref="I2:N2"/>
     <mergeCell ref="O2:V2"/>
-    <mergeCell ref="W1:AB1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="W3:AB3"/>
-    <mergeCell ref="O1:V1"/>
-    <mergeCell ref="I1:N1"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="I3:N3"/>
+    <mergeCell ref="AC3:AH3"/>
     <mergeCell ref="F3:H3"/>
-    <mergeCell ref="W2:AB2"/>
-    <mergeCell ref="AC3:AH3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6406,7 +6466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ77"/>
+  <dimension ref="A1:BQ80"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -7668,7 +7728,7 @@
       <c r="BP14" s="10" t="n"/>
       <c r="BQ14" s="11" t="n"/>
     </row>
-    <row r="15" ht="416" customHeight="1">
+    <row r="15" ht="448" customHeight="1">
       <c r="A15" s="44" t="n">
         <v>3</v>
       </c>
@@ -7692,8 +7752,9 @@
         <is>
           <t>・role: CHUOKAI
 ・ログイン済 + MFA認証済
-・自中央会と管轄 JA が事前にデータベース上に登録済み
-・テストデータ：自中央会のファイル 2 件、管轄 JA のファイル 2 件、管轄外 JA のファイル 2 件、全 JA 向けファイル（`ja_id IS NULL`）1 件</t>
+・自中央会と同一都道府県の JA、他県の JA が事前にデータベース上に登録済み
+・セッションに `todofuken_code` が設定されていること
+・テストデータ：自 JA のファイル 2 件、**同一都道府県の他 JA** のファイル 2 件、**他県 JA** のファイル 2 件、全 JA 向けファイル（`ja_id IS NULL`）1 件</t>
         </is>
       </c>
       <c r="K15" s="10" t="n"/>
@@ -7752,7 +7813,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>管轄外 JA のファイル（`ja_id` がスコープ外）を直接ダウンロード API GET `/api/v1/file-download/{file_download_id}/download` で呼び出し</t>
+            <t>他県 JA のファイル（`ja_id` がスコープ外）を直接ダウンロード API GET `/api/v1/file-download/{file_download_id}/download` で呼び出し</t>
           </r>
         </is>
       </c>
@@ -7795,7 +7856,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">自中央会のファイル + 管轄 JA のファイル + 全 JA 向けファイル（合計 5 件）のみ返却されること、管轄外 JA のファイルが含まれないこと
+            <t xml:space="preserve">自 JA のファイル + **同一都道府県の他 JA** のファイル + 全 JA 向けファイル（合計 5 件）のみ返却されること、他県 JA のファイルが含まれないこと（顧客要件2026-07 / #52132 で「自JAのみ」から拡大）
 </t>
           </r>
           <r>
@@ -8631,7 +8692,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・日農ロール（NICHINO_ADMIN 役割1 / NICHINO_STAFF 役割2）は `nichino_download_allowed_flg = false` のファイルをダウンロード / プレビュー不可
+            <t xml:space="preserve">・**DL制限ロール**（NICHINO_ADMIN 役割1 / NICHINO_STAFF 役割2 / **CHUOKAI 役割3**）は `nichino_download_allowed_flg = false` のファイルをダウンロード / プレビュー不可（中央会の追加は顧客要件2026-07）。ただし**自分が出力したファイルは本フラグを見ない**（#52132・ACSMS-TC-022-060 参照）
 </t>
           </r>
           <r>
@@ -8647,7 +8708,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>・行 disabled 条件：(a) 論理削除済（`deleted_at ≠ NULL`）OR (b) 日農ロール かつ `nichino_download_allowed_flg = false`</t>
+            <t>・行 disabled 条件：(a) 論理削除済（`deleted_at ≠ NULL`）OR (b) DL制限ロール（日農 + 中央会）かつ `nichino_download_allowed_flg = false` かつ **自分が出力したファイルでない**</t>
           </r>
         </is>
       </c>
@@ -8881,7 +8942,7 @@
       <c r="BP20" s="10" t="n"/>
       <c r="BQ20" s="11" t="n"/>
     </row>
-    <row r="21" ht="400" customHeight="1">
+    <row r="21" ht="432" customHeight="1">
       <c r="A21" s="44" t="n">
         <v>9</v>
       </c>
@@ -9007,7 +9068,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>・`nichino_download_allowed_flg` は日農ロール（役割1 / 役割2）のみに作用する制御であり、JA系ロール（CHUOKAI / JA_HONTEN / JA_KANRI_SHITEN）は自身の DataScope 範囲内であればフラグ値に関わらずダウンロード / プレビュー可能であること</t>
+            <t>・`nichino_download_allowed_flg` はDL制限ロール（日農 役割1 / 役割2 + **中央会 役割3**）に作用する制御であり、JA_HONTEN / JA_KANRI_SHITEN は自身の DataScope 範囲内であればフラグ値に関わらずダウンロード / プレビュー可能であること。中央会は顧客要件2026-07 で制限対象に追加された（ACSMS-TC-022-060 参照）</t>
           </r>
         </is>
       </c>
@@ -19681,8 +19742,867 @@
       <c r="BP77" s="10" t="n"/>
       <c r="BQ77" s="11" t="n"/>
     </row>
+    <row r="78" ht="22.5" customHeight="1">
+      <c r="A78" s="32" t="inlineStr">
+        <is>
+          <t>DataScope拡大・DL許可の例外（Scope / Download Gate）</t>
+        </is>
+      </c>
+      <c r="B78" s="10" t="n"/>
+      <c r="C78" s="10" t="n"/>
+      <c r="D78" s="10" t="n"/>
+      <c r="E78" s="10" t="n"/>
+      <c r="F78" s="10" t="n"/>
+      <c r="G78" s="10" t="n"/>
+      <c r="H78" s="10" t="n"/>
+      <c r="I78" s="10" t="n"/>
+      <c r="J78" s="10" t="n"/>
+      <c r="K78" s="10" t="n"/>
+      <c r="L78" s="10" t="n"/>
+      <c r="M78" s="10" t="n"/>
+      <c r="N78" s="10" t="n"/>
+      <c r="O78" s="10" t="n"/>
+      <c r="P78" s="10" t="n"/>
+      <c r="Q78" s="10" t="n"/>
+      <c r="R78" s="10" t="n"/>
+      <c r="S78" s="10" t="n"/>
+      <c r="T78" s="10" t="n"/>
+      <c r="U78" s="10" t="n"/>
+      <c r="V78" s="10" t="n"/>
+      <c r="W78" s="10" t="n"/>
+      <c r="X78" s="10" t="n"/>
+      <c r="Y78" s="10" t="n"/>
+      <c r="Z78" s="10" t="n"/>
+      <c r="AA78" s="10" t="n"/>
+      <c r="AB78" s="10" t="n"/>
+      <c r="AC78" s="10" t="n"/>
+      <c r="AD78" s="10" t="n"/>
+      <c r="AE78" s="10" t="n"/>
+      <c r="AF78" s="10" t="n"/>
+      <c r="AG78" s="10" t="n"/>
+      <c r="AH78" s="10" t="n"/>
+      <c r="AI78" s="10" t="n"/>
+      <c r="AJ78" s="10" t="n"/>
+      <c r="AK78" s="10" t="n"/>
+      <c r="AL78" s="10" t="n"/>
+      <c r="AM78" s="10" t="n"/>
+      <c r="AN78" s="10" t="n"/>
+      <c r="AO78" s="10" t="n"/>
+      <c r="AP78" s="10" t="n"/>
+      <c r="AQ78" s="10" t="n"/>
+      <c r="AR78" s="10" t="n"/>
+      <c r="AS78" s="10" t="n"/>
+      <c r="AT78" s="10" t="n"/>
+      <c r="AU78" s="10" t="n"/>
+      <c r="AV78" s="10" t="n"/>
+      <c r="AW78" s="10" t="n"/>
+      <c r="AX78" s="10" t="n"/>
+      <c r="AY78" s="10" t="n"/>
+      <c r="AZ78" s="10" t="n"/>
+      <c r="BA78" s="10" t="n"/>
+      <c r="BB78" s="10" t="n"/>
+      <c r="BC78" s="10" t="n"/>
+      <c r="BD78" s="10" t="n"/>
+      <c r="BE78" s="10" t="n"/>
+      <c r="BF78" s="10" t="n"/>
+      <c r="BG78" s="10" t="n"/>
+      <c r="BH78" s="10" t="n"/>
+      <c r="BI78" s="10" t="n"/>
+      <c r="BJ78" s="10" t="n"/>
+      <c r="BK78" s="10" t="n"/>
+      <c r="BL78" s="10" t="n"/>
+      <c r="BM78" s="10" t="n"/>
+      <c r="BN78" s="10" t="n"/>
+      <c r="BO78" s="10" t="n"/>
+      <c r="BP78" s="10" t="n"/>
+      <c r="BQ78" s="11" t="n"/>
+    </row>
+    <row r="79" ht="450" customHeight="1">
+      <c r="A79" s="44" t="n">
+        <v>59</v>
+      </c>
+      <c r="B79" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-022-059</t>
+        </is>
+      </c>
+      <c r="C79" s="10" t="n"/>
+      <c r="D79" s="11" t="n"/>
+      <c r="E79" s="46" t="inlineStr">
+        <is>
+          <t>中央会のDataScope拡大 — 同一都道府県の全JA（#52132）</t>
+        </is>
+      </c>
+      <c r="F79" s="10" t="n"/>
+      <c r="G79" s="10" t="n"/>
+      <c r="H79" s="10" t="n"/>
+      <c r="I79" s="11" t="n"/>
+      <c r="J79" s="46" t="inlineStr">
+        <is>
+          <t>・role: CHUOKAI（自JA=ja_id 5、`todofuken_code='13'`）
+・同一都道府県（13）に自JA以外のJAが 2 件存在し、それぞれファイルを出力済み
+・他県（例：14）のJAのファイルが 1 件存在する
+・同県他JAのファイルには `nichino_download_allowed_flg = true` のものと `false` のものを両方用意する
+・`todofuken_code` を**持たない**セッション（本機能デプロイ前に発行されたもの）も用意する</t>
+        </is>
+      </c>
+      <c r="K79" s="10" t="n"/>
+      <c r="L79" s="10" t="n"/>
+      <c r="M79" s="10" t="n"/>
+      <c r="N79" s="10" t="n"/>
+      <c r="O79" s="10" t="n"/>
+      <c r="P79" s="11" t="n"/>
+      <c r="Q79" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">一覧を表示し、返却されるファイルの `ja_id` を確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">JA絞り込みプルダウンの候補を確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">都道府県プルダウンの状態を確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">同県他JAのファイル（`nichino_download_allowed_flg = true`）を個別ダウンロード・プレビュー・ZIP一括でそれぞれ取得する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">同県他JAのファイル（`nichino_download_allowed_flg = false`）を個別ダウンロードする
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ6：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">他県JAのファイルの `file_download_id` を直接指定してダウンロードAPIを呼び出す
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ7：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">`todofuken_code` を持たないセッションで一覧を表示する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ8：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>role が JA_HONTEN / JA_KANRI_SHITEN のアカウント（`todofuken_code` を持つ）で一覧を表示する</t>
+          </r>
+        </is>
+      </c>
+      <c r="R79" s="10" t="n"/>
+      <c r="S79" s="10" t="n"/>
+      <c r="T79" s="10" t="n"/>
+      <c r="U79" s="10" t="n"/>
+      <c r="V79" s="10" t="n"/>
+      <c r="W79" s="11" t="n"/>
+      <c r="X79" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">自JA + 同県他JA2件 + 全JA向け（`ja_id IS NULL`）のファイルが返ること。他県JAのファイルは含まれないこと
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">自県の全JAが候補として表示されること（`GET /api/v1/ja/dropdown?scope=todofuken`）。他県のJAは候補に出ないこと
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">都道府県が**自県で固定**されていること（他県は選択できない）。BE 側でも他県は弾かれるため、選ばせない方針
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">いずれも成功すること。**一覧に出た行は個別ダウンロード・プレビュー・ZIPでも通る**こと（同じ ja_id 集合で判定する不変条件）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">HTTPステータスコード403（`FORBIDDEN`、メッセージ `このファイルは日農のダウンロードが許可されていません。`）が返ること。**一覧には見えるがDLはできない**（スコープ判定とDL可否判定は別）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ6：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">HTTPステータスコード404（`NOT_FOUND`）が返ること（スコープ外は存在隠蔽）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ7：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">**自JAのファイルのみ**が返ること（従来動作へフォールバック）。エラーにはならないこと
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ8：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">自JAのファイルのみが返ること。`todofuken_code` を持っていても県内全JAへは広がらないこと
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・拡大先の県は**クライアント指定ではなくセッションの `todofuken_code`** から決まるため、他県を覗くことはできない
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・`todofuken_code` を optional 扱いにしているのは、本機能のデプロイ前に発行された Redis 上の既存セッションに当該項目が存在しないため。必須型にすると実行時の実態と食い違う
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・判定を `role_code = CHUOKAI` に限定しているのは、JA_HONTEN / JA_KANRI_SHITEN も `todofuken_code` を持つため。コードの有無だけで分岐すると両ロールまで県内全JAへ広がる（ステップ8がその回帰確認）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・FE で JA絞り込みを自JA固定＋disable のままにすると検索条件が常に `ja_id = 自JA` となり、BE の拡大が一切効かない（ステップ2がその回帰確認）</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y79" s="10" t="n"/>
+      <c r="Z79" s="10" t="n"/>
+      <c r="AA79" s="10" t="n"/>
+      <c r="AB79" s="10" t="n"/>
+      <c r="AC79" s="10" t="n"/>
+      <c r="AD79" s="11" t="n"/>
+      <c r="AE79" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF79" s="11" t="n"/>
+      <c r="AG79" s="45" t="inlineStr"/>
+      <c r="AH79" s="10" t="n"/>
+      <c r="AI79" s="11" t="n"/>
+      <c r="AJ79" s="45" t="inlineStr"/>
+      <c r="AK79" s="10" t="n"/>
+      <c r="AL79" s="11" t="n"/>
+      <c r="AM79" s="45" t="inlineStr"/>
+      <c r="AN79" s="10" t="n"/>
+      <c r="AO79" s="11" t="n"/>
+      <c r="AP79" s="45" t="inlineStr"/>
+      <c r="AQ79" s="10" t="n"/>
+      <c r="AR79" s="11" t="n"/>
+      <c r="AS79" s="45" t="inlineStr"/>
+      <c r="AT79" s="10" t="n"/>
+      <c r="AU79" s="11" t="n"/>
+      <c r="AV79" s="45" t="inlineStr"/>
+      <c r="AW79" s="10" t="n"/>
+      <c r="AX79" s="11" t="n"/>
+      <c r="AY79" s="45" t="inlineStr"/>
+      <c r="AZ79" s="10" t="n"/>
+      <c r="BA79" s="11" t="n"/>
+      <c r="BB79" s="45" t="inlineStr"/>
+      <c r="BC79" s="10" t="n"/>
+      <c r="BD79" s="11" t="n"/>
+      <c r="BE79" s="45" t="inlineStr"/>
+      <c r="BF79" s="10" t="n"/>
+      <c r="BG79" s="11" t="n"/>
+      <c r="BH79" s="45" t="inlineStr"/>
+      <c r="BI79" s="10" t="n"/>
+      <c r="BJ79" s="11" t="n"/>
+      <c r="BK79" s="46" t="inlineStr"/>
+      <c r="BL79" s="10" t="n"/>
+      <c r="BM79" s="10" t="n"/>
+      <c r="BN79" s="10" t="n"/>
+      <c r="BO79" s="10" t="n"/>
+      <c r="BP79" s="10" t="n"/>
+      <c r="BQ79" s="11" t="n"/>
+    </row>
+    <row r="80" ht="450" customHeight="1">
+      <c r="A80" s="44" t="n">
+        <v>60</v>
+      </c>
+      <c r="B80" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-022-060</t>
+        </is>
+      </c>
+      <c r="C80" s="10" t="n"/>
+      <c r="D80" s="11" t="n"/>
+      <c r="E80" s="46" t="inlineStr">
+        <is>
+          <t>日農DL許可 — 対象ロールへの中央会追加と、自作成ファイルの例外（#52132）</t>
+        </is>
+      </c>
+      <c r="F80" s="10" t="n"/>
+      <c r="G80" s="10" t="n"/>
+      <c r="H80" s="10" t="n"/>
+      <c r="I80" s="11" t="n"/>
+      <c r="J80" s="46" t="inlineStr">
+        <is>
+          <t>・以下のファイルを用意すること
+・(a) `nichino_download_allowed_flg = false`・`created_by` = **他アカウント**
+・(b) `nichino_download_allowed_flg = false`・`created_by` = **ログイン中のアカウントの `account_id`**
+・(c) `nichino_download_allowed_flg = false`・`created_by` = **空文字**
+・(d) `nichino_download_allowed_flg = true`・`created_by` = 他アカウント
+・role: NICHINO_ADMIN / NICHINO_STAFF / CHUOKAI / JA_HONTEN / JA_KANRI_SHITEN の各アカウント</t>
+        </is>
+      </c>
+      <c r="K80" s="10" t="n"/>
+      <c r="L80" s="10" t="n"/>
+      <c r="M80" s="10" t="n"/>
+      <c r="N80" s="10" t="n"/>
+      <c r="O80" s="10" t="n"/>
+      <c r="P80" s="11" t="n"/>
+      <c r="Q80" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">CHUOKAI で一覧を表示し、(a)〜(d) の行の無効化（チェックボックス・ファイル名リンク）状態を確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">CHUOKAI で (a) をダウンロード／プレビューする
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">CHUOKAI で (b) をダウンロードする
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">CHUOKAI で (c) をダウンロードする
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">NICHINO_ADMIN / NICHINO_STAFF でも (a) が403、(b) が成功することを確認する
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ6：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">JA_HONTEN / JA_KANRI_SHITEN で (a) をダウンロードする
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ7：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>(a) を含む複数ファイルを選択してZIP一括ダウンロードする</t>
+          </r>
+        </is>
+      </c>
+      <c r="R80" s="10" t="n"/>
+      <c r="S80" s="10" t="n"/>
+      <c r="T80" s="10" t="n"/>
+      <c r="U80" s="10" t="n"/>
+      <c r="V80" s="10" t="n"/>
+      <c r="W80" s="11" t="n"/>
+      <c r="X80" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">(a) と (c) が無効化されること。**(b) は無効化されないこと**（自分が出力したファイル）。(d) は無効化されないこと
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">HTTPステータスコード403（`FORBIDDEN`、メッセージ `このファイルは日農のダウンロードが許可されていません。`）が返ること。中央会が対象ロールに追加されている（顧客要件2026-07。従来は日農のみ）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">**ダウンロードが成功すること**。本フラグは「他組織へ自組織のファイルを見せてよいか」を JA 側が決めるもので、出力した本人まで締め出す意図は無い
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">403が返ること（`created_by` が空文字の行は**本人扱いしない**＝安全側に倒す）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ5：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">例外はDL制限3ロール共通であること（中央会だけの特例ではない）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ6：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ダウンロードが成功すること（JA系ロールは本フラグの影響を受けない）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ7：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">403となり、ZIPが生成されないこと（ZIPも個別DLと同じチェックを通る）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・既定値が FALSE のため、この例外が無いと中央会が自分で出力した帳票をその場でダウンロードできなかった（#52132 の発端）
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・本人判定は `t_file_download.created_by`（`m_account.account_id` を varchar で保持）で行い、両辺を trim 済み文字列に揃えて突合する。一覧SQLの `m_account.account_id::text = fd.created_by` と同じ前提
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・行は一覧に表示されるため、存在を隠す404ではなく403を返す</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y80" s="10" t="n"/>
+      <c r="Z80" s="10" t="n"/>
+      <c r="AA80" s="10" t="n"/>
+      <c r="AB80" s="10" t="n"/>
+      <c r="AC80" s="10" t="n"/>
+      <c r="AD80" s="11" t="n"/>
+      <c r="AE80" s="45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AF80" s="11" t="n"/>
+      <c r="AG80" s="45" t="inlineStr"/>
+      <c r="AH80" s="10" t="n"/>
+      <c r="AI80" s="11" t="n"/>
+      <c r="AJ80" s="45" t="inlineStr"/>
+      <c r="AK80" s="10" t="n"/>
+      <c r="AL80" s="11" t="n"/>
+      <c r="AM80" s="45" t="inlineStr"/>
+      <c r="AN80" s="10" t="n"/>
+      <c r="AO80" s="11" t="n"/>
+      <c r="AP80" s="45" t="inlineStr"/>
+      <c r="AQ80" s="10" t="n"/>
+      <c r="AR80" s="11" t="n"/>
+      <c r="AS80" s="45" t="inlineStr"/>
+      <c r="AT80" s="10" t="n"/>
+      <c r="AU80" s="11" t="n"/>
+      <c r="AV80" s="45" t="inlineStr"/>
+      <c r="AW80" s="10" t="n"/>
+      <c r="AX80" s="11" t="n"/>
+      <c r="AY80" s="45" t="inlineStr"/>
+      <c r="AZ80" s="10" t="n"/>
+      <c r="BA80" s="11" t="n"/>
+      <c r="BB80" s="45" t="inlineStr"/>
+      <c r="BC80" s="10" t="n"/>
+      <c r="BD80" s="11" t="n"/>
+      <c r="BE80" s="45" t="inlineStr"/>
+      <c r="BF80" s="10" t="n"/>
+      <c r="BG80" s="11" t="n"/>
+      <c r="BH80" s="45" t="inlineStr"/>
+      <c r="BI80" s="10" t="n"/>
+      <c r="BJ80" s="11" t="n"/>
+      <c r="BK80" s="46" t="inlineStr">
+        <is>
+          <t>(なし)
+---</t>
+        </is>
+      </c>
+      <c r="BL80" s="10" t="n"/>
+      <c r="BM80" s="10" t="n"/>
+      <c r="BN80" s="10" t="n"/>
+      <c r="BO80" s="10" t="n"/>
+      <c r="BP80" s="10" t="n"/>
+      <c r="BQ80" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="1060">
+  <mergeCells count="1095">
     <mergeCell ref="AS59:AU59"/>
     <mergeCell ref="J31:P31"/>
     <mergeCell ref="B60:D60"/>
@@ -19718,6 +20638,7 @@
     <mergeCell ref="J57:P57"/>
     <mergeCell ref="W2:AH2"/>
     <mergeCell ref="BB77:BD77"/>
+    <mergeCell ref="B80:D80"/>
     <mergeCell ref="X10:AD11"/>
     <mergeCell ref="AG42:AI42"/>
     <mergeCell ref="BK70:BQ70"/>
@@ -19744,6 +20665,7 @@
     <mergeCell ref="Q15:W15"/>
     <mergeCell ref="AV39:AX39"/>
     <mergeCell ref="AV70:AX70"/>
+    <mergeCell ref="AP79:AR79"/>
     <mergeCell ref="BE20:BG20"/>
     <mergeCell ref="BH21:BJ21"/>
     <mergeCell ref="AM34:AO34"/>
@@ -19787,6 +20709,7 @@
     <mergeCell ref="AV63:AX63"/>
     <mergeCell ref="AP66:AR66"/>
     <mergeCell ref="BH49:BJ49"/>
+    <mergeCell ref="E80:I80"/>
     <mergeCell ref="R3:V3"/>
     <mergeCell ref="BK66:BQ66"/>
     <mergeCell ref="X16:AD16"/>
@@ -19806,6 +20729,7 @@
     <mergeCell ref="AG50:AI50"/>
     <mergeCell ref="AP67:AR67"/>
     <mergeCell ref="BK13:BQ13"/>
+    <mergeCell ref="BE79:BG79"/>
     <mergeCell ref="B21:D21"/>
     <mergeCell ref="AY57:BA57"/>
     <mergeCell ref="BE41:BG41"/>
@@ -19823,6 +20747,7 @@
     <mergeCell ref="Q61:W61"/>
     <mergeCell ref="W3:AH3"/>
     <mergeCell ref="Q48:W48"/>
+    <mergeCell ref="BK79:BQ79"/>
     <mergeCell ref="AE75:AF75"/>
     <mergeCell ref="AV13:AX13"/>
     <mergeCell ref="BH42:BJ42"/>
@@ -19851,9 +20776,11 @@
     <mergeCell ref="BE34:BG34"/>
     <mergeCell ref="BE28:BG28"/>
     <mergeCell ref="AJ41:AL41"/>
+    <mergeCell ref="AM80:AO80"/>
     <mergeCell ref="H8:J8"/>
     <mergeCell ref="BK10:BQ11"/>
     <mergeCell ref="AS14:AU14"/>
+    <mergeCell ref="AM79:AO79"/>
     <mergeCell ref="AG55:AI55"/>
     <mergeCell ref="AP18:AR18"/>
     <mergeCell ref="AJ56:AL56"/>
@@ -19862,6 +20789,7 @@
     <mergeCell ref="BE30:BG30"/>
     <mergeCell ref="AG38:AI38"/>
     <mergeCell ref="AY70:BA70"/>
+    <mergeCell ref="J80:P80"/>
     <mergeCell ref="AV25:AX25"/>
     <mergeCell ref="W6:Y6"/>
     <mergeCell ref="J55:P55"/>
@@ -19915,6 +20843,7 @@
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="E49:I49"/>
     <mergeCell ref="J68:P68"/>
+    <mergeCell ref="AV79:AX79"/>
     <mergeCell ref="AY18:BA18"/>
     <mergeCell ref="A7:G7"/>
     <mergeCell ref="AY45:BA45"/>
@@ -19932,6 +20861,7 @@
     <mergeCell ref="BH32:BJ32"/>
     <mergeCell ref="BK18:BQ18"/>
     <mergeCell ref="B27:D27"/>
+    <mergeCell ref="AE80:AF80"/>
     <mergeCell ref="BH47:BJ47"/>
     <mergeCell ref="X20:AD20"/>
     <mergeCell ref="BH74:BJ74"/>
@@ -20035,6 +20965,7 @@
     <mergeCell ref="AM31:AO31"/>
     <mergeCell ref="BE39:BG39"/>
     <mergeCell ref="BE70:BG70"/>
+    <mergeCell ref="AY79:BA79"/>
     <mergeCell ref="X48:AD48"/>
     <mergeCell ref="AE23:AF23"/>
     <mergeCell ref="AC6:AE6"/>
@@ -20067,6 +20998,7 @@
     <mergeCell ref="J26:P26"/>
     <mergeCell ref="BH66:BJ66"/>
     <mergeCell ref="AS41:AU41"/>
+    <mergeCell ref="AV80:AX80"/>
     <mergeCell ref="AE49:AF49"/>
     <mergeCell ref="AY13:BA13"/>
     <mergeCell ref="Q8:S8"/>
@@ -20081,6 +21013,7 @@
     <mergeCell ref="AP38:AR38"/>
     <mergeCell ref="X41:AD41"/>
     <mergeCell ref="BH68:BJ68"/>
+    <mergeCell ref="Q80:W80"/>
     <mergeCell ref="AE76:AF76"/>
     <mergeCell ref="AY63:BA63"/>
     <mergeCell ref="BE25:BG25"/>
@@ -20107,11 +21040,13 @@
     <mergeCell ref="X36:AD36"/>
     <mergeCell ref="J52:P52"/>
     <mergeCell ref="AE77:AF77"/>
+    <mergeCell ref="AJ80:AL80"/>
     <mergeCell ref="J44:P44"/>
     <mergeCell ref="Q25:W25"/>
     <mergeCell ref="AV37:AX37"/>
     <mergeCell ref="BB65:BD65"/>
     <mergeCell ref="BE66:BG66"/>
+    <mergeCell ref="AJ79:AL79"/>
     <mergeCell ref="E60:I60"/>
     <mergeCell ref="Q71:W71"/>
     <mergeCell ref="X67:AD67"/>
@@ -20137,6 +21072,7 @@
     <mergeCell ref="AM23:AO23"/>
     <mergeCell ref="AE24:AF24"/>
     <mergeCell ref="J70:P70"/>
+    <mergeCell ref="BE80:BG80"/>
     <mergeCell ref="AS44:AU44"/>
     <mergeCell ref="AV27:AX27"/>
     <mergeCell ref="BE55:BG55"/>
@@ -20163,6 +21099,7 @@
     <mergeCell ref="AP30:AR30"/>
     <mergeCell ref="J76:P76"/>
     <mergeCell ref="AP59:AR59"/>
+    <mergeCell ref="E79:I79"/>
     <mergeCell ref="AJ30:AL30"/>
     <mergeCell ref="E73:I73"/>
     <mergeCell ref="AP46:AR46"/>
@@ -20176,6 +21113,7 @@
     <mergeCell ref="Q21:W21"/>
     <mergeCell ref="AP61:AR61"/>
     <mergeCell ref="AM16:AO16"/>
+    <mergeCell ref="BB80:BD80"/>
     <mergeCell ref="AP48:AR48"/>
     <mergeCell ref="B64:D64"/>
     <mergeCell ref="AE44:AF44"/>
@@ -20204,6 +21142,7 @@
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="E66:I66"/>
     <mergeCell ref="AV71:AX71"/>
+    <mergeCell ref="J79:P79"/>
     <mergeCell ref="AE70:AF70"/>
     <mergeCell ref="AY72:BA72"/>
     <mergeCell ref="AM48:AO48"/>
@@ -20217,6 +21156,7 @@
     <mergeCell ref="B57:D57"/>
     <mergeCell ref="AF6:AH6"/>
     <mergeCell ref="E55:I55"/>
+    <mergeCell ref="AG80:AI80"/>
     <mergeCell ref="AE32:AF32"/>
     <mergeCell ref="AV48:AX48"/>
     <mergeCell ref="E67:I67"/>
@@ -20334,6 +21274,7 @@
     <mergeCell ref="AE48:AF48"/>
     <mergeCell ref="AP75:AR75"/>
     <mergeCell ref="BH27:BJ27"/>
+    <mergeCell ref="AS80:AU80"/>
     <mergeCell ref="BK75:BQ75"/>
     <mergeCell ref="AS55:AU55"/>
     <mergeCell ref="BE37:BG37"/>
@@ -20412,6 +21353,7 @@
     <mergeCell ref="Q50:W50"/>
     <mergeCell ref="AM72:AO72"/>
     <mergeCell ref="AJ27:AL27"/>
+    <mergeCell ref="AS79:AU79"/>
     <mergeCell ref="AY41:BA41"/>
     <mergeCell ref="X15:AD15"/>
     <mergeCell ref="AV18:AX18"/>
@@ -20422,6 +21364,7 @@
     <mergeCell ref="AV11:AX11"/>
     <mergeCell ref="AP20:AR20"/>
     <mergeCell ref="AS21:AU21"/>
+    <mergeCell ref="X79:AD79"/>
     <mergeCell ref="BE32:BG32"/>
     <mergeCell ref="BE63:BG63"/>
     <mergeCell ref="BK14:BQ14"/>
@@ -20448,6 +21391,8 @@
     <mergeCell ref="AJ45:AL45"/>
     <mergeCell ref="AG57:AI57"/>
     <mergeCell ref="E63:I63"/>
+    <mergeCell ref="AP80:AR80"/>
+    <mergeCell ref="BK80:BQ80"/>
     <mergeCell ref="B15:D15"/>
     <mergeCell ref="BB52:BD52"/>
     <mergeCell ref="AJ55:AL55"/>
@@ -20458,6 +21403,7 @@
     <mergeCell ref="AY25:BA25"/>
     <mergeCell ref="AS34:AU34"/>
     <mergeCell ref="BB45:BD45"/>
+    <mergeCell ref="B79:D79"/>
     <mergeCell ref="BB32:BD32"/>
     <mergeCell ref="Q55:W55"/>
     <mergeCell ref="A33:BQ33"/>
@@ -20536,11 +21482,13 @@
     <mergeCell ref="AJ21:AL21"/>
     <mergeCell ref="J27:P27"/>
     <mergeCell ref="AG25:AI25"/>
+    <mergeCell ref="Q79:W79"/>
     <mergeCell ref="T5:AH5"/>
     <mergeCell ref="AP23:AR23"/>
     <mergeCell ref="B56:D56"/>
     <mergeCell ref="AJ61:AL61"/>
     <mergeCell ref="J20:P20"/>
+    <mergeCell ref="BH80:BJ80"/>
     <mergeCell ref="AV47:AX47"/>
     <mergeCell ref="AY75:BA75"/>
     <mergeCell ref="BE51:BG51"/>
@@ -20562,6 +21510,7 @@
     <mergeCell ref="X31:AD31"/>
     <mergeCell ref="Q10:W11"/>
     <mergeCell ref="BB25:BD25"/>
+    <mergeCell ref="A78:BQ78"/>
     <mergeCell ref="AP49:AR49"/>
     <mergeCell ref="E28:I28"/>
     <mergeCell ref="BH57:BJ57"/>
@@ -20601,6 +21550,7 @@
     <mergeCell ref="Q67:W67"/>
     <mergeCell ref="AG73:AI73"/>
     <mergeCell ref="B75:D75"/>
+    <mergeCell ref="AG79:AI79"/>
     <mergeCell ref="A29:BQ29"/>
     <mergeCell ref="AV35:AX35"/>
     <mergeCell ref="AJ11:AL11"/>
@@ -20634,9 +21584,11 @@
     <mergeCell ref="AM68:AO68"/>
     <mergeCell ref="BH52:BJ52"/>
     <mergeCell ref="AS27:AU27"/>
+    <mergeCell ref="BH79:BJ79"/>
     <mergeCell ref="AP31:AR31"/>
     <mergeCell ref="AE35:AF35"/>
     <mergeCell ref="BH14:BJ14"/>
+    <mergeCell ref="BB79:BD79"/>
     <mergeCell ref="BK54:BQ54"/>
     <mergeCell ref="AJ62:AL62"/>
     <mergeCell ref="AJ37:AL37"/>
@@ -20667,6 +21619,7 @@
     <mergeCell ref="J30:P30"/>
     <mergeCell ref="AV41:AX41"/>
     <mergeCell ref="AE13:AF13"/>
+    <mergeCell ref="AY80:BA80"/>
     <mergeCell ref="AS45:AU45"/>
     <mergeCell ref="BK57:BQ57"/>
     <mergeCell ref="AE40:AF40"/>
@@ -20687,6 +21640,7 @@
     <mergeCell ref="AM62:AO62"/>
     <mergeCell ref="J54:P54"/>
     <mergeCell ref="BB74:BD74"/>
+    <mergeCell ref="AE79:AF79"/>
     <mergeCell ref="J41:P41"/>
     <mergeCell ref="Q44:W44"/>
     <mergeCell ref="BB67:BD67"/>
@@ -20743,15 +21697,16 @@
     <mergeCell ref="E75:I75"/>
     <mergeCell ref="BE60:BG60"/>
     <mergeCell ref="AG77:AI77"/>
+    <mergeCell ref="X80:AD80"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="AE13:AE21 AE23:AE28 AE30:AE32 AE34:AE42 AE44:AE52 AE54:AE57 AE59:AE68 AE70:AE77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AE13:AE21 AE23:AE28 AE30:AE32 AE34:AE42 AE44:AE52 AE54:AE57 AE59:AE68 AE70:AE77 AE79:AE80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N,A,B"</formula1>
     </dataValidation>
-    <dataValidation sqref="AG13:AG21 AG23:AG28 AG30:AG32 AG34:AG42 AG44:AG52 AG54:AG57 AG59:AG68 AG70:AG77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AG13:AG21 AG23:AG28 AG30:AG32 AG34:AG42 AG44:AG52 AG54:AG57 AG59:AG68 AG70:AG77 AG79:AG80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="AV13:AV21 AV23:AV28 AV30:AV32 AV34:AV42 AV44:AV52 AV54:AV57 AV59:AV68 AV70:AV77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AV13:AV21 AV23:AV28 AV30:AV32 AV34:AV42 AV44:AV52 AV54:AV57 AV59:AV68 AV70:AV77 AV79:AV80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
     <dataValidation sqref="F1" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
